--- a/data/content/senses_table_tem8_merged.xlsx
+++ b/data/content/senses_table_tem8_merged.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -487,7 +487,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>análisis</t>
+          <t>cita</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,32 +497,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>预约；（也指）约会</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>El análisis del discurso revela cómo los conectores organizan la argumentación en un editorial.</t>
+          <t>Pedí una cita en la oficina de extranjeros para renovar mi tarjeta de residencia.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>话语分析揭示连接词如何在社论中组织论证结构。</t>
+          <t>我预约了外国人事务办公室去续居留卡。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>images/analisis_1.jpg</t>
+          <t>images/cita_1.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bilingüismo</t>
+          <t>autonomía</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,44 +544,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>双语能力；双语现象</t>
+          <t>自治；自治权；自主；独立</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>El bilingüismo no implica dominio perfecto de ambas lenguas en todos los registros.</t>
+          <t>La universidad goza de cierta autonomía para decidir sus propios planes de estudio.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>双语并不意味着两种语言在一切语体上都完美精通。</t>
+          <t>大学在决定自己的教学计划方面享有一定的自治权。</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>images/bilinguismo_1.jpg</t>
+          <t>images/autonomia_1.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>coherencia</t>
+          <t>ortografía</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -591,44 +591,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>连贯；条理</t>
+          <t>拼写</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>La coherencia textual depende de que cada párrafo avance la idea central sin contradicciones.</t>
+          <t>Cuidar la ortografía incluye tildes y la diferencia entre b/v o g/j según la regla.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>篇章连贯取决于每一段推进中心思想且不自相矛盾。</t>
+          <t>注意拼写包括重音符号，以及按规则区分 b/v、g/j 等。</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>images/coherencia_1.jpg</t>
+          <t>images/ortografia_1.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cohesión</t>
+          <t>presupuesto</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -638,44 +638,44 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>衔接（语言学术语）</t>
+          <t>预算</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Los pronombres y los conectores aportan cohesión al unir oraciones dentro del mismo párrafo.</t>
+          <t>Haz un presupuesto mensual: comida, transporte, material de estudio y un pequeño ahorro.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>代词与连接词通过把句间关系连起来，带来篇章衔接。</t>
+          <t>做一份月预算：吃饭、交通、学习用品和一点储蓄。</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>images/cohesion_1.jpg</t>
+          <t>images/presupuesto_1.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>competencia</t>
+          <t>traducción</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -685,54 +685,54 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>能力；（语言）能力</t>
+          <t>翻译</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>La competencia comunicativa incluye saber qué decir, cómo decirlo y cuándo callar.</t>
+          <t>La traducción no es solo cambiar palabras: hay que respetar el sentido y el tono del texto original.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>交际能力包括知道说什么、怎么说，以及何时保持沉默。</t>
+          <t>翻译不只是换词，还要尊重原文的意义与语气。</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>images/competencia_1.jpg</t>
+          <t>images/traduccion_1.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>competencia</t>
+          <t>acusación</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -742,22 +742,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>竞争；竞赛</t>
+          <t>指控；控告</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>La competencia entre empresas tecnológicas acelera la innovación, pero también genera presión laboral.</t>
+          <t>La acusación carece de pruebas suficientes.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>科技企业间的竞争加速创新，但也带来职场压力。</t>
+          <t>该指控缺乏足够证据。</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>images/competencia_2.jpg</t>
+          <t>images/acusacion_1.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>conclusión</t>
+          <t>afirmación</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -789,22 +789,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>结论</t>
+          <t>断言；肯定说法</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>En la conclusión no introduzcas datos nuevos; resume y señala límites o futuras líneas de trabajo.</t>
+          <t>Su afirmación no se sostiene con los datos.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>结论部分不要引入新数据；应总结并指出局限或未来研究方向。</t>
+          <t>他的断言得不到数据支撑。</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>images/conclusion_1.jpg</t>
+          <t>images/afirmacion_1.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>crítica</t>
+          <t>alusión</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -836,22 +836,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>评论；批评</t>
+          <t>暗指；典故式提及</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>La crítica literaria no solo juzga si un libro «gusta», sino cómo construye sentido y estilo.</t>
+          <t>El texto hace una alusión a Cervantes.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>文学批评不只判断书是否「好看」，还分析它如何构建意义与风格。</t>
+          <t>文本暗指塞万提斯。</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>images/critica_1.jpg</t>
+          <t>images/alusion_1.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>discurso</t>
+          <t>analogía</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -883,22 +883,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>话语；演说</t>
+          <t>类比</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El discurso político usa metáforas y repeticiones para persuadir a una audiencia diversa.</t>
+          <t>Usa una analogía para explicar el concepto.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>政治演说运用隐喻与重复，以说服多元听众。</t>
+          <t>他用类比解释该概念。</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>images/discurso_1.jpg</t>
+          <t>images/analogia_1.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>diversidad</t>
+          <t>anexo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -930,22 +930,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>多样性</t>
+          <t>附录</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>La diversidad lingüística del mundo hispánico es un patrimonio que conviene preservar y estudiar.</t>
+          <t>Los datos completos figuran en el anexo.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>西语世界的语言多样性是值得保护与研究的遗产。</t>
+          <t>完整数据见附录。</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>images/diversidad_1.jpg</t>
+          <t>images/anexo_1.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -957,7 +957,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>enfoque</t>
+          <t>antonimia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -977,22 +977,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>切入角度；方法焦点</t>
+          <t>反义关系</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El enfoque comunicativo prioriza el uso real de la lengua frente a la memorización de reglas.</t>
+          <t>Alto/bajo es un ejemplo clásico de antonimia gradable.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>交际法优先真实使用语言，而非死记规则。</t>
+          <t>高/低是典型的可分级反义。</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>images/enfoque_1.jpg</t>
+          <t>images/antonimia_1.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>estilo</t>
+          <t>análisis</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1024,34 +1024,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>风格；文风</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El estilo del autor se reconoce por frases largas, adjetivos precisos y un humor contenido.</t>
+          <t>El análisis del discurso revela cómo los conectores organizan la argumentación en un editorial.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>作者的文风以长句、精确形容词与克制的幽默为特征。</t>
+          <t>话语分析揭示连接词如何在社论中组织论证结构。</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>images/estilo_1.jpg</t>
+          <t>images/analisis_1.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fuente</t>
+          <t>aproximación</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1071,22 +1071,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>来源；（也指）泉水</t>
+          <t>方法；进路；接近</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cita siempre la fuente primaria cuando uses datos estadísticos en tu trabajo de investigación.</t>
+          <t>Proponemos una aproximación interdisciplinaria.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>在研究作业中使用统计数据时，务必引用原始来源。</t>
+          <t>我们提出跨学科进路。</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>images/fuente_1.jpg</t>
+          <t>images/aproximacion_1.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1098,17 +1098,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fuente</t>
+          <t>argumentación</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1118,22 +1118,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>泉水；喷泉</t>
+          <t>论证；论述</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nos sentamos junto a la fuente de la plaza mientras repasábamos las preguntas del examen oral.</t>
+          <t>La argumentación del ensayo debe presentar pruebas y contraargumentos.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>我们坐在广场喷泉旁复习口语考试的问题。</t>
+          <t>论文的论证应提出证据与反驳。</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>images/fuente_2.jpg</t>
+          <t>images/argumentacion_1.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1145,7 +1145,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>globalización</t>
+          <t>arqueología</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1165,22 +1165,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>全球化</t>
+          <t>考古学</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>La globalización facilita el intercambio cultural, aunque también plantea retos a las identidades locales.</t>
+          <t>La arqueología aporta datos materiales sobre el pasado.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>全球化促进文化交流，同时也给地方认同带来挑战。</t>
+          <t>考古学为过去提供物质证据。</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>images/globalizacion_1.jpg</t>
+          <t>images/arqueologia_1.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1192,7 +1192,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hipótesis</t>
+          <t>artefacto</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1212,22 +1212,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>假设；假说</t>
+          <t>人工制品；产物</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>La hipótesis del estudio sostiene que el contacto frecuente con hablantes nativos acelera la fluidez.</t>
+          <t>El texto es un artefacto cultural de su época.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>该研究假设：与母语者频繁接触会加快流利度提升。</t>
+          <t>文本是其时代的文化产物。</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>images/hipotesis_1.jpg</t>
+          <t>images/artefacto_1.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1239,7 +1239,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>homónimo</t>
+          <t>bilingüismo</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1259,22 +1259,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>同音/同形异义词</t>
+          <t>双语能力；双语现象</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>«Banco» (asiento) y «banco» (entidad financiera) son homónimos: misma forma, sentidos distintos.</t>
+          <t>El bilingüismo no implica dominio perfecto de ambas lenguas en todos los registros.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>banco（长凳）与 banco（金融机构）是同形异义词：形式相同、意义不同。</t>
+          <t>双语并不意味着两种语言在一切语体上都完美精通。</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>images/homonimo_1.jpg</t>
+          <t>images/bilinguismo_1.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1286,7 +1286,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>identidad</t>
+          <t>categoría</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1306,22 +1306,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>身份；认同</t>
+          <t>范畴；类别</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>La identidad cultural se construye con la lengua, la memoria familiar y las prácticas cotidianas.</t>
+          <t>Hay que definir cada categoría con precisión.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>文化认同由语言、家庭记忆与日常实践共同建构。</t>
+          <t>必须精确界定每一范畴。</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>images/identidad_1.jpg</t>
+          <t>images/categoria_1.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>inferencia</t>
+          <t>causalidad</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1353,22 +1353,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>推断；推理</t>
+          <t>因果关系</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aunque el texto no lo diga explícitamente, por inferencia entendemos que el personaje está en crisis.</t>
+          <t>Correlación no implica necesariamente causalidad.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>虽然文本未明说，通过推断我们明白人物正陷入危机。</t>
+          <t>相关并不必然意味着因果。</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>images/inferencia_1.jpg</t>
+          <t>images/causalidad_1.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1380,7 +1380,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>innovación</t>
+          <t>cláusula</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1400,22 +1400,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>创新</t>
+          <t>从句；条款</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>La innovación educativa no es solo usar apps, sino rediseñar actividades para un aprendizaje activo.</t>
+          <t>Analiza la cláusula subordinada del periodo.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>教育创新不只是用 App，而是重新设计活动以促进主动学习。</t>
+          <t>分析该句中的从属从句。</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>images/innovacion_1.jpg</t>
+          <t>images/clausula_1.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ironía</t>
+          <t>codificación</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1447,22 +1447,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>反讽；讽刺</t>
+          <t>编码</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>La ironía del personaje aparece cuando dice lo contrario de lo que realmente piensa.</t>
+          <t>La codificación de los datos sigue un protocolo.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>当人物说的与真实想法相反时，反讽便出现了。</t>
+          <t>数据编码遵循协议。</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>images/ironia_1.jpg</t>
+          <t>images/codificacion_1.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1474,7 +1474,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>metodología</t>
+          <t>cognición</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1494,22 +1494,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>方法论；方法</t>
+          <t>认知</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>La metodología combina análisis cuantitativo de corpus y entrevistas cualitativas a aprendices.</t>
+          <t>La cognición humana procesa el lenguaje en red.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>该方法论结合语料库定量分析与对学习者的定性访谈。</t>
+          <t>人类认知以网络方式处理语言。</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>images/metodologia_1.jpg</t>
+          <t>images/cognicion_1.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>metáfora</t>
+          <t>coherencia</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>隐喻</t>
+          <t>连贯；条理</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La metáfora «el tiempo es oro» presenta el tiempo como un recurso valioso que no debe malgastarse.</t>
+          <t>La coherencia textual depende de que cada párrafo avance la idea central sin contradicciones.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>隐喻「时间就是金钱」把时间呈现为不应浪费的宝贵资源。</t>
+          <t>篇章连贯取决于每一段推进中心思想且不自相矛盾。</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>images/metafora_1.jpg</t>
+          <t>images/coherencia_1.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>migración</t>
+          <t>cohesión</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1588,22 +1588,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>移民；迁徙</t>
+          <t>衔接（语言学术语）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>La migración por estudios es común entre universitarios que buscan experiencias internacionales.</t>
+          <t>Los pronombres y los conectores aportan cohesión al unir oraciones dentro del mismo párrafo.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>出于求学原因的迁移在寻求国际体验的大学生中很常见。</t>
+          <t>代词与连接词通过把句间关系连起来，带来篇章衔接。</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>images/migracion_1.jpg</t>
+          <t>images/cohesion_1.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1615,7 +1615,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>narrativa</t>
+          <t>colonización</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1635,22 +1635,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>叙事；叙事作品</t>
+          <t>殖民</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>En la narrativa contemporánea el narrador a veces es poco fiable y obliga al lector a interpretar.</t>
+          <t>La colonización dejó huellas lingüísticas profundas.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>在当代叙事中，叙述者有时不可靠，迫使读者自行解读。</t>
+          <t>殖民留下深刻的语言痕迹。</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>images/narrativa_1.jpg</t>
+          <t>images/colonizacion_1.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1662,7 +1662,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>patrimonio</t>
+          <t>competencia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1682,22 +1682,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>遗产（文化）</t>
+          <t>能力；（语言）能力</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>El patrimonio inmaterial incluye danzas, oficios y saberes transmitidos de generación en generación.</t>
+          <t>La competencia comunicativa incluye saber qué decir, cómo decirlo y cuándo callar.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>非物质文化遗产包括代代相传的舞蹈、手艺与知识。</t>
+          <t>交际能力包括知道说什么、怎么说，以及何时保持沉默。</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>images/patrimonio_1.jpg</t>
+          <t>images/competencia_1.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1709,17 +1709,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>perspectiva</t>
+          <t>competencia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1729,22 +1729,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>视角；观点</t>
+          <t>竞争；竞赛</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cambiar de perspectiva nos hace ver el conflicto desde el lado de las personas afectadas.</t>
+          <t>La competencia entre empresas tecnológicas acelera la innovación, pero también genera presión laboral.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>转换视角能让我们从受影响者一方去看这场冲突。</t>
+          <t>科技企业间的竞争加速创新，但也带来职场压力。</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>images/perspectiva_1.jpg</t>
+          <t>images/competencia_2.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>precisión</t>
+          <t>complejidad</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1776,22 +1776,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>精确；精准</t>
+          <t>复杂性</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>La precisión léxica distingue a un texto avanzado de una redacción solo «comprensible».</t>
+          <t>La complejidad del fenómeno exige varios enfoques.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>词汇精确度把高级文本与仅仅「能看懂」的作文区分开。</t>
+          <t>现象的复杂性要求多种方法。</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>images/precision_1.jpg</t>
+          <t>images/complejidad_1.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>registro académico</t>
+          <t>compromiso</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1823,22 +1823,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>学术语体</t>
+          <t>承诺；介入</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>En el registro académico evitamos muletillas y preferimos conectores como «por consiguiente».</t>
+          <t>El texto muestra un compromiso ético.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>学术语体中我们避免口头禅，更偏好「因此」一类连接词。</t>
+          <t>文本显示出伦理介入。</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>images/registro_academico_1.jpg</t>
+          <t>images/compromiso_1.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1850,7 +1850,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>reseña</t>
+          <t>conciliación</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1870,22 +1870,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>书评；简介性评论</t>
+          <t>调解；和解</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>La reseña resume la trama sin spoilers y valora el ritmo, los personajes y el lenguaje.</t>
+          <t>Buscan la conciliación de intereses opuestos.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>书评概括情节但不剧透，并评价节奏、人物与语言。</t>
+          <t>他们寻求对立利益的和解。</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>images/resena_1.jpg</t>
+          <t>images/conciliacion_1.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sostenibilidad</t>
+          <t>conclusión</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1917,22 +1917,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>可持续性</t>
+          <t>结论</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>La sostenibilidad urbana exige transporte público eficiente y espacios verdes accesibles.</t>
+          <t>En la conclusión no introduzcas datos nuevos; resume y señala límites o futuras líneas de trabajo.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>城市可持续性要求高效公交与市民可达的绿色空间。</t>
+          <t>结论部分不要引入新数据；应总结并指出局限或未来研究方向。</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>images/sostenibilidad_1.jpg</t>
+          <t>images/conclusion_1.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1944,7 +1944,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>terminología</t>
+          <t>configuración</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1964,22 +1964,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>术语</t>
+          <t>构型；配置</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dominar la terminología especializada es necesario para leer artículos científicos con precisión.</t>
+          <t>Analizamos la configuración del relato.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>要精确阅读科研文章，必须掌握专业术语。</t>
+          <t>我们分析叙事构型。</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>images/terminologia_1.jpg</t>
+          <t>images/configuracion_1.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1991,7 +1991,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tesis</t>
+          <t>consenso</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2011,22 +2011,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>论点；（亦指）学位论文</t>
+          <t>共识</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>La tesis del artículo afirma que el subtitulado favorece el aprendizaje incidental de vocabulario.</t>
+          <t>No hay consenso sobre la definición.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>文章的论点是：字幕有利于词汇的附带习得。</t>
+          <t>关于定义尚无共识。</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>images/tesis_1.jpg</t>
+          <t>images/consenso_1.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2038,7 +2038,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ética</t>
+          <t>consistencia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2058,22 +2058,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>伦理</t>
+          <t>一致性；连贯严谨</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>La ética periodística exige verificar fuentes antes de publicar una acusación grave.</t>
+          <t>La consistencia argumentativa es esencial.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>新闻伦理要求在刊发严重指控前核实消息来源。</t>
+          <t>论证一致性至关重要。</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>images/etica_1.jpg</t>
+          <t>images/consistencia_1.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2085,7 +2085,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>contaminación</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2095,32 +2095,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>摘要（学术论文）</t>
+          <t>污染；（也指）干扰</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>El abstract debe condensar objetivos, método, resultados y conclusión en un párrafo denso.</t>
+          <t>Hay contaminación entre variedades en contacto.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>摘要需在紧凑一段中概括目标、方法、结果与结论。</t>
+          <t>接触中的变体之间存在干扰。</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>images/abstract_1.jpg</t>
+          <t>images/contaminacion_1.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>alegoría</t>
+          <t>contextualizar</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2142,32 +2142,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>v</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>寓言；讽喻</t>
+          <t>置于语境；语境化</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>En la alegoría cada elemento del relato representa una idea abstracta sobre la sociedad.</t>
+          <t>Hay que contextualizar la cita antes de analizarla.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>在寓言/讽喻中，故事里每个元素都象征某种关于社会的抽象观念。</t>
+          <t>分析引文前须先置于语境。</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>images/alegoria_1.jpg</t>
+          <t>images/contextualizar_1.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2179,7 +2179,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ambigüedad</t>
+          <t>contradicción</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2189,32 +2189,32 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>歧义；含混</t>
+          <t>矛盾</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>La ambigüedad deliberada en el poema permite varias lecturas sin una interpretación única.</t>
+          <t>El texto cae en contradicción entre el primer y el último párrafo.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>诗中故意的含混允许多种解读，而非单一解释。</t>
+          <t>文本在首段与末段之间自相矛盾。</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>images/ambiguedad_1.jpg</t>
+          <t>images/contradiccion_1.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2226,7 +2226,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>colocación</t>
+          <t>contraposición</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2236,32 +2236,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>搭配（词汇学）</t>
+          <t>对照；对立设置</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Es más natural decir «tomar una decisión» que «hacer una decisión»; eso es una colocación.</t>
+          <t>La contraposición de personajes estructura la novela.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>说 tomar una decisión 比 hacer una decisión 更自然，这就是搭配。</t>
+          <t>人物对照构成小说结构。</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>images/colocacion_1.jpg</t>
+          <t>images/contraposicion_1.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2273,7 +2273,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>concisión</t>
+          <t>convención</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2283,32 +2283,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>简洁</t>
+          <t>惯例；公约</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>La concisión no significa empobrecer el estilo, sino eliminar repeticiones innecesarias.</t>
+          <t>Rompe la convención narrativa del final cerrado.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>简洁并不意味着风格贫乏，而是去掉不必要的重复。</t>
+          <t>它打破封闭结局的叙事惯例。</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>images/concision_1.jpg</t>
+          <t>images/convencion_1.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2320,7 +2320,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>corpus</t>
+          <t>correlación</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2330,32 +2330,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>语料库</t>
+          <t>相关；相关性</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>El corpus digital permite observar frecuencias reales de uso y colocaciones frecuentes.</t>
+          <t>Hay correlación entre horas de estudio y rendimiento.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>数字语料库能观察真实使用频率与常见搭配。</t>
+          <t>学习时长与成绩之间存在相关。</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>images/corpus_1.jpg</t>
+          <t>images/correlacion_1.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>etimología</t>
+          <t>corroborar</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2377,32 +2377,32 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>v</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>词源</t>
+          <t>证实；确证</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>La etimología de muchas palabras españolas remonta al latín y, en algunos casos, al árabe.</t>
+          <t>Los datos corroboran la hipótesis.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>许多西语词的词源可追溯到拉丁语，有些则来自阿拉伯语。</t>
+          <t>数据证实了该假设。</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>images/etimologia_1.jpg</t>
+          <t>images/corroborar_1.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2414,7 +2414,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>eufemismo</t>
+          <t>credibilidad</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2424,32 +2424,32 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>委婉语</t>
+          <t>可信度</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Decir «tercer edad» en lugar de expresiones peyorativas es un eufemismo social común.</t>
+          <t>La fuente pierde credibilidad sin referencias.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>用「terce edad / 老年」替代贬损说法，是常见的社会委婉语。</t>
+          <t>缺少出处会降低来源可信度。</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>images/eufemismo_1.jpg</t>
+          <t>images/credibilidad_1.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>hegemonía</t>
+          <t>criterio</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2471,44 +2471,44 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>霸权；主导地位</t>
+          <t>标准；准则</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Algunos autores hablan de hegemonía cultural cuando ciertos relatos dominan el espacio mediático.</t>
+          <t>Hay que definir criterios claros de evaluación.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>某些作者称，当特定叙事主导媒体空间时，便存在文化霸权。</t>
+          <t>必须明确评价标准。</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>images/hegemonia_1.jpg</t>
+          <t>images/criterio_1.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ideología</t>
+          <t>crítica</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2518,32 +2518,32 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>意识形态</t>
+          <t>评论；批评</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>El ensayo examina cómo la ideología se infiltra en las elecciones léxicas de un texto periodístico.</t>
+          <t>La crítica literaria no solo juzga si un libro «gusta», sino cómo construye sentido y estilo.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>这篇文章检视意识形态如何渗透进新闻文本的用词选择。</t>
+          <t>文学批评不只判断书是否「好看」，还分析它如何构建意义与风格。</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>images/ideologia_1.jpg</t>
+          <t>images/critica_1.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2555,7 +2555,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>implicatura</t>
+          <t>cuestionario</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2565,32 +2565,32 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>会话含义（语用学）</t>
+          <t>问卷</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>La implicatura surge cuando el oyente deduce un sentido no dicho a partir del contexto conversacional.</t>
+          <t>El cuestionario mide actitudes lingüísticas.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>当听者根据会话语境推出未明说的含义时，便产生会话含义。</t>
+          <t>问卷测量语言态度。</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>images/implicatura_1.jpg</t>
+          <t>images/cuestionario_1.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>intertextualidad</t>
+          <t>deducción</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2612,44 +2612,44 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>互文性</t>
+          <t>演绎</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>La intertextualidad aparece cuando la novela cita, transforma o dialoga con obras anteriores.</t>
+          <t>La deducción parte de premisas generales.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>当小说引用、改写或与先前作品对话时，便出现互文性。</t>
+          <t>演绎从一般前提出发。</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>images/intertextualidad_1.jpg</t>
+          <t>images/deduccion_1.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>matiz</t>
+          <t>delimitación</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2659,32 +2659,32 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>细微差别；语感差别</t>
+          <t>界定；划界</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hay un matiz importante entre «pedir» y «solicitar»: el segundo suele ser más formal.</t>
+          <t>La delimitación del objeto de estudio es clave.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>pedir 与 solicitar 有重要细微差别：后者通常更正式。</t>
+          <t>研究对象的界定很关键。</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>images/matiz_1.jpg</t>
+          <t>images/delimitacion_1.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2696,7 +2696,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>memoria histórica</t>
+          <t>demografía</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2706,32 +2706,32 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>历史记忆</t>
+          <t>人口学；人口结构</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>El debate sobre la memoria histórica examina cómo una sociedad recuerda conflictos del pasado.</t>
+          <t>La demografía explica cambios en el uso lingüístico.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>关于历史记忆的讨论审视一个社会如何铭记过去的冲突。</t>
+          <t>人口结构解释语言使用变化。</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>images/memoria_historica_1.jpg</t>
+          <t>images/demografia_1.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2743,7 +2743,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>paradigma</t>
+          <t>desplazamiento</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2753,32 +2753,32 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>范式</t>
+          <t>迁移；转移</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>El nuevo paradigma educativo pone al estudiante como centro del proceso de aprendizaje.</t>
+          <t>El desplazamiento semántico altera el significado.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>新的教育范式把学生置于学习过程的中心。</t>
+          <t>语义转移改变意义。</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>images/paradigma_1.jpg</t>
+          <t>images/desplazamiento_1.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2790,7 +2790,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>polisemia</t>
+          <t>dialecto</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2800,32 +2800,32 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>多义性</t>
+          <t>方言</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>La polisemia de «banco» incluye el asiento y la institución financiera según el contexto.</t>
+          <t>El andaluz es un dialecto del español peninsular.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>banco 的多义性包括「长凳」与「银行」，取决于语境。</t>
+          <t>安达卢西亚语是半岛西班牙语的一种方言。</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>images/polisemia_1.jpg</t>
+          <t>images/dialecto_1.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2837,7 +2837,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>pragmatismo</t>
+          <t>dicotomía</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2847,32 +2847,32 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>实用主义；（亦指）务实态度</t>
+          <t>二分法</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Con pragmatismo, la institución eligió un plan viable en lugar de una reforma ideal pero imposible.</t>
+          <t>Evita una dicotomía demasiado rígida.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>出于务实，该机构选择了可行方案，而非理想却不可行的改革。</t>
+          <t>避免过于僵硬的二分。</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>images/pragmatismo_1.jpg</t>
+          <t>images/dicotomia_1.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2884,7 +2884,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>préstamo lingüístico</t>
+          <t>diferenciación</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2894,32 +2894,32 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>借词</t>
+          <t>分化；区分</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>«Fútbol» es un préstamo lingüístico del inglés que se ha adaptado a la ortografía española.</t>
+          <t>Hay diferenciación estilística entre géneros.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>fútbol 是来自英语的借词，并已适应西语拼写。</t>
+          <t>体裁之间存在风格分化。</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>images/prestamo_linguistico_1.jpg</t>
+          <t>images/diferenciacion_1.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2931,7 +2931,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>redundancia</t>
+          <t>discurso</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2941,32 +2941,32 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>冗余；重复累赘</t>
+          <t>话语；演说</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Evita la redundancia del tipo «subir hacia arriba»; una sola idea basta si ya está clara.</t>
+          <t>El discurso político usa metáforas y repeticiones para persuadir a una audiencia diversa.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>避免「向上爬升」这类冗余；意思已清楚时说一遍即可。</t>
+          <t>政治演说运用隐喻与重复，以说服多元听众。</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>images/redundancia_1.jpg</t>
+          <t>images/discurso_1.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sesgo</t>
+          <t>distribución</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2988,32 +2988,32 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>偏见；偏差</t>
+          <t>分布</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Detectar el sesgo en un artículo implica observar qué voces se citan y cuáles se omiten.</t>
+          <t>Estudiamos la distribución geográfica del rasgo.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>识别文章中的偏见，要看引用了哪些声音、又忽略了哪些。</t>
+          <t>我们研究该特征的地理分布。</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>images/sesgo_1.jpg</t>
+          <t>images/distribucion_1.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3025,7 +3025,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>simbolismo</t>
+          <t>divergencia</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3035,32 +3035,32 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>象征手法；象征主义</t>
+          <t>分歧；分化</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>El simbolismo del río en la novela sugiere transformación y el paso irreversible del tiempo.</t>
+          <t>La divergencia dialectal aumenta con la distancia.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>小说中河流的象征暗示转变与时间的不可逆流逝。</t>
+          <t>方言分歧随距离增大。</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>images/simbolismo_1.jpg</t>
+          <t>images/divergencia_1.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3072,7 +3072,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>sociolingüística</t>
+          <t>diversidad</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3082,32 +3082,32 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>社会语言学</t>
+          <t>多样性</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>La sociolingüística estudia cómo la clase social, la edad y el género influyen en el habla.</t>
+          <t>La diversidad lingüística del mundo hispánico es un patrimonio que conviene preservar y estudiar.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>社会语言学研究社会阶层、年龄与性别如何影响言语。</t>
+          <t>西语世界的语言多样性是值得保护与研究的遗产。</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>images/sociolinguistica_1.jpg</t>
+          <t>images/diversidad_1.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>tabú lingüístico</t>
+          <t>documentación</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3129,32 +3129,32 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>语言禁忌</t>
+          <t>文献；文档工作</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>El tabú lingüístico explica por qué ciertas palabras se evitan en contextos formales o familiares.</t>
+          <t>La documentación de lenguas en peligro es urgente.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>语言禁忌解释了为何某些词在正式或家庭语境中会被回避。</t>
+          <t>濒危语言文献工作紧迫。</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>images/tabu_linguistico_1.jpg</t>
+          <t>images/documentacion_1.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3166,42 +3166,42 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>tesis</t>
+          <t>elaboración</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>学位论文</t>
+          <t>加工；阐述</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Defendió su tesis doctoral ante un tribunal tras cinco años de investigación de archivo.</t>
+          <t>La elaboración del argumento requiere ejemplos.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>经过五年档案研究，她在答辩委员会前进行了博士论文答辩。</t>
+          <t>论证的阐述需要例子。</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>images/tesis_2.jpg</t>
+          <t>images/elaboracion_1.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3213,45 +3213,6672 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>elipsis</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>省略</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>La elipsis evita repeticiones innecesarias.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>省略避免不必要的重复。</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>images/elipsis_1.jpg</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>empatía</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>共情</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>La empatía del narrador acerca al lector.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>叙述者的共情拉近读者。</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>images/empatia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>encuesta</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>调查</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>La encuesta recoge datos de percepción.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>调查收集感知数据。</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>images/encuesta_1.jpg</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>enfoque</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>切入角度；方法焦点</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>El enfoque comunicativo prioriza el uso real de la lengua frente a la memorización de reglas.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>交际法优先真实使用语言，而非死记规则。</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>images/enfoque_1.jpg</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>entorno</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>环境；语境环境</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>El entorno sociolingüístico condiciona el habla.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>社会语言环境制约说话方式。</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>images/entorno_1.jpg</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>enumeración</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>列举</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>La enumeración refuerza la idea principal.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>列举强化中心思想。</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>images/enumeracion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>enunciado</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>表述；话语单位</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Cada enunciado realiza un acto de habla en contexto.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>每个表述在语境中完成一个言语行为。</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>images/enunciado_1.jpg</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>equivalencia</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>对等</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Busca equivalencia funcional en la traducción.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>翻译中寻求功能对等。</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>images/equivalencia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>escala</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>量表；尺度</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Usamos una escala Likert de cinco puntos.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>我们使用五点李克特量表。</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>images/escala_1.jpg</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>estabilidad</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>稳定性</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>La norma busca estabilidad ortográfica.</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>规范追求拼写稳定。</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>images/estabilidad_1.jpg</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>estigma</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>污名</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>El estigma lingüístico afecta a hablantes.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>语言污名影响使用者。</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>images/estigma_1.jpg</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>estilo</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>风格；文风</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>El estilo del autor se reconoce por frases largas, adjetivos precisos y un humor contenido.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>作者的文风以长句、精确形容词与克制的幽默为特征。</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>images/estilo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>etnografía</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>民族志</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>La etnografía observa prácticas situadas.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>民族志观察情境中的实践。</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>images/etnografia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>evaluación</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>评价；评估</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>La evaluación formativa guía el aprendizaje.</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>形成性评价引导学习。</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>images/evaluacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>专八|专四</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>evidencia</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>La evidencia empírica respalda la hipótesis principal.</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>经验证据支持主要假设。</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>images/evidencia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>expectativa</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>期待</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Rompe la expectativa del lector.</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>它打破了读者的期待。</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>images/expectativa_1.jpg</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>explicación</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>解释</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>La explicación aclara el procedimiento.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>解释澄清了步骤。</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>images/explicacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>exposición</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>说明文；陈述</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>La exposición presenta hechos con claridad.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>说明文清晰陈述事实。</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>images/exposicion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>专八|专四</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>fiabilidad</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>信度</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Comprobamos la fiabilidad del instrumento.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>我们检验工具信度。</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>images/fiabilidad_1.jpg</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>fonética</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>语音学</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>La fonética describe cómo se producen los sonidos.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>语音学描述语音如何发出。</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>images/fonetica_1.jpg</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>fragmentación</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>碎片化</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>La fragmentación narrativa refleja crisis.</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>叙事碎片化反映危机。</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>images/fragmentacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>来源；（也指）泉水</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Cita siempre la fuente primaria cuando uses datos estadísticos en tu trabajo de investigación.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>在研究作业中使用统计数据时，务必引用原始来源。</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>images/fuente_1.jpg</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>泉水；喷泉</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Nos sentamos junto a la fuente de la plaza mientras repasábamos las preguntas del examen oral.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>我们坐在广场喷泉旁复习口语考试的问题。</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>images/fuente_2.jpg</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>generalización</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>概括</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Evita generalizaciones apresuradas.</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>避免仓促概括。</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>images/generalizacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>globalización</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>全球化</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>La globalización facilita el intercambio cultural, aunque también plantea retos a las identidades locales.</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>全球化促进文化交流，同时也给地方认同带来挑战。</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>images/globalizacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>glosario</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>术语表</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>El glosario define los términos técnicos del capítulo.</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>术语表界定本章技术用语。</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>images/glosario_1.jpg</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>hipotético</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>adj</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>假设的；假想的</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Partimos de un escenario hipotético para el debate.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>我们从假想情景展开辩论。</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>images/hipotetico_1.jpg</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>hipótesis</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>假设；假说</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>La hipótesis del estudio sostiene que el contacto frecuente con hablantes nativos acelera la fluidez.</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>该研究假设：与母语者频繁接触会加快流利度提升。</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>images/hipotesis_1.jpg</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>homónimo</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>同音/同形异义词</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>«Banco» (asiento) y «banco» (entidad financiera) son homónimos: misma forma, sentidos distintos.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>banco（长凳）与 banco（金融机构）是同形异义词：形式相同、意义不同。</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>images/homonimo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>identidad</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>身份；认同</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>La identidad cultural se construye con la lengua, la memoria familiar y las prácticas cotidianas.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>文化认同由语言、家庭记忆与日常实践共同建构。</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>images/identidad_1.jpg</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>inferencia</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>推断；推理</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Aunque el texto no lo diga explícitamente, por inferencia entendemos que el personaje está en crisis.</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>虽然文本未明说，通过推断我们明白人物正陷入危机。</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>images/inferencia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>innovación</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>创新</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>La innovación educativa no es solo usar apps, sino rediseñar actividades para un aprendizaje activo.</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>教育创新不只是用 App，而是重新设计活动以促进主动学习。</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>images/innovacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>interpretación</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>口译；解读</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Su interpretación del poema destaca el tono irónico.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>他对这首诗的解读突出了反讽语气。</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>images/interpretacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>专八|专四</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ironía</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>反讽；讽刺</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>La ironía del personaje aparece cuando dice lo contrario de lo que realmente piensa.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>当人物说的与真实想法相反时，反讽便出现了。</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>images/ironia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>matizar</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>细化；限定说法</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Conviene matizar la afirmación para no generalizar en exceso.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>宜对说法加以限定，以免过度概括。</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>images/matizar_1.jpg</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>metodología</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>方法论；方法</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>La metodología combina análisis cuantitativo de corpus y entrevistas cualitativas a aprendices.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>该方法论结合语料库定量分析与对学习者的定性访谈。</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>images/metodologia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>metáfora</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>隐喻</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>La metáfora «el tiempo es oro» presenta el tiempo como un recurso valioso que no debe malgastarse.</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>隐喻「时间就是金钱」把时间呈现为不应浪费的宝贵资源。</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>images/metafora_1.jpg</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>migración</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>移民；迁徙</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>La migración por estudios es común entre universitarios que buscan experiencias internacionales.</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>出于求学原因的迁移在寻求国际体验的大学生中很常见。</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>images/migracion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>morfema</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>词素</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>«-ción» es un morfema derivativo frecuente en español.</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-ción 是西班牙语中常见的派生词素。</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>images/morfema_1.jpg</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>morfología</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>形态学</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>La morfología analiza raíces, prefijos y sufijos.</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>形态学分析词根、前缀与后缀。</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>images/morfologia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>narrativa</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>叙事；叙事作品</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>En la narrativa contemporánea el narrador a veces es poco fiable y obliga al lector a interpretar.</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>在当代叙事中，叙述者有时不可靠，迫使读者自行解读。</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>images/narrativa_1.jpg</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>neologismo</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>新词</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>«Selfie» es un neologismo que se ha extendido globalmente.</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>selfie 是一个已全球流行的新词。</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>images/neologismo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>paráfrasis</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>释义；改写</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Haz una paráfrasis del párrafo sin copiar las mismas palabras.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>用不同措辞改写该段，不要照抄原词。</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>images/parafrasis_1.jpg</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>patrimonio</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>遗产（文化）</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>El patrimonio inmaterial incluye danzas, oficios y saberes transmitidos de generación en generación.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>非物质文化遗产包括代代相传的舞蹈、手艺与知识。</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>images/patrimonio_1.jpg</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>perspectiva</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>视角；观点</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Cambiar de perspectiva nos hace ver el conflicto desde el lado de las personas afectadas.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>转换视角能让我们从受影响者一方去看这场冲突。</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>images/perspectiva_1.jpg</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>persuasión</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>说服；劝说</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>La publicidad usa estrategias de persuasión visual y verbal.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>广告运用视觉与语言的说服策略。</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>images/persuasion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>pragmática</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>语用学</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>La pragmática estudia cómo el contexto afecta el significado.</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>语用学研究语境如何影响意义。</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>images/pragmatica_1.jpg</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>precisión</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>精确；精准</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>La precisión léxica distingue a un texto avanzado de una redacción solo «comprensible».</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>词汇精确度把高级文本与仅仅「能看懂」的作文区分开。</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>images/precision_1.jpg</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>refutación</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>反驳；驳论</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>La refutación ocupa el tercer párrafo del ensayo.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>驳论占据文章第三段。</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>images/refutacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>refutar</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>反驳</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>El autor intenta refutar la hipótesis rival con datos nuevos.</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>作者试图用新数据反驳对立假设。</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>images/refutar_1.jpg</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>registro académico</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>学术语体</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>En el registro académico evitamos muletillas y preferimos conectores como «por consiguiente».</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>学术语体中我们避免口头禅，更偏好「因此」一类连接词。</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>images/registro_academico_1.jpg</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>reseña</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>书评；简介性评论</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>La reseña resume la trama sin spoilers y valora el ritmo, los personajes y el lenguaje.</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>书评概括情节但不剧透，并评价节奏、人物与语言。</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>images/resena_1.jpg</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>semántica</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>语义学</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>La semántica estudia el significado de las palabras y oraciones.</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>语义学研究词与句的意义。</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>images/semantica_1.jpg</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>sinonimia</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>同义关系</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>La sinonimia absoluta es rara: casi siempre hay matices.</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>绝对同义很少见：几乎总有细微差别。</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>images/sinonimia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>sintaxis</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>句法学；句法</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>La sintaxis describe cómo se combinan las palabras en la oración.</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>句法学描述词语如何组成句子。</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>images/sintaxis_1.jpg</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>sostenibilidad</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>可持续性</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>La sostenibilidad urbana exige transporte público eficiente y espacios verdes accesibles.</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>城市可持续性要求高效公交与市民可达的绿色空间。</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>images/sostenibilidad_1.jpg</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>síntesis</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>综合；综述</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>La síntesis reúne las ideas principales sin detalles superfluos.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>综述汇总主要观点，不含多余细节。</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>images/sintesis_1.jpg</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>专八|专四</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>terminología</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>术语</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Dominar la terminología especializada es necesario para leer artículos científicos con precisión.</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>要精确阅读科研文章，必须掌握专业术语。</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>images/terminologia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>tesis</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>论点；（亦指）学位论文</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>La tesis del artículo afirma que el subtitulado favorece el aprendizaje incidental de vocabulario.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>文章的论点是：字幕有利于词汇的附带习得。</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>images/tesis_1.jpg</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>tipología</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>类型学；分类</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>La tipología textual distingue narración, descripción y argumentación.</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>语篇类型学区分叙述、描写与论证。</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>images/tipologia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>variación</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>变异；变体差异</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>La variación dialectal se observa en el léxico y la pronunciación.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>方言变异体现在词汇与发音上。</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>images/variacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ética</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>伦理</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>La ética periodística exige verificar fuentes antes de publicar una acusación grave.</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>新闻伦理要求在刊发严重指控前核实消息来源。</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>images/etica_1.jpg</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>abstracción</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>抽象；抽象化</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>La abstracción permite generalizar a partir de casos concretos.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>抽象使人能从具体案例中概括。</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>images/abstraccion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>摘要（学术论文）</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>El abstract debe condensar objetivos, método, resultados y conclusión en un párrafo denso.</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>摘要需在紧凑一段中概括目标、方法、结果与结论。</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>images/abstract_1.jpg</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>alegato</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>申辩；陈词</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>El abogado presentó un alegato contundente.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>律师提出了有力申辩。</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>images/alegato_1.jpg</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>alegoría</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>寓言；讽喻</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>En la alegoría cada elemento del relato representa una idea abstracta sobre la sociedad.</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>在寓言/讽喻中，故事里每个元素都象征某种关于社会的抽象观念。</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>images/alegoria_1.jpg</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ambigüedad</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>歧义；含混</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>La ambigüedad deliberada en el poema permite varias lecturas sin una interpretación única.</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>诗中故意的含混允许多种解读，而非单一解释。</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>images/ambiguedad_1.jpg</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>antagonismo</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>对立；拮抗</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Hay un claro antagonismo entre ambas posturas.</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>两种立场之间存在明显对立。</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>images/antagonismo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>análisis crítico</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>批判性分析</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>El análisis crítico examina supuestos ideológicos.</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>批判性分析审视意识形态前提。</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>images/analisis_critico_1.jpg</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>apología</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>辩护文；颂扬</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>El ensayo es una apología del multiculturalismo.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>这篇论文是对多元文化主义的辩护。</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>images/apologia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>asimetría</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>不对称</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>La asimetría de poder marca el diálogo.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>权力不对称塑造了对话。</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>images/asimetria_1.jpg</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>axiología</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>价值论</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>La axiología estudia los sistemas de valores.</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>价值论研究价值体系。</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>images/axiologia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>axioma</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>公理；基本命题</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Partimos de un axioma que no se discute en este marco.</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>我们从本框架内不讨论的公理出发。</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>images/axioma_1.jpg</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>canónico</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>adj</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>经典的；正典的</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Forma parte del corpus canónico de la literatura.</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>它属于文学正典语料。</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>images/canonico_1.jpg</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>categorización</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>范畴化</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>La categorización social influye en el discurso.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>社会范畴化影响话语。</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>images/categorizacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>coacción</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>胁迫；强制</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>El consentimiento no es válido bajo coacción.</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>胁迫下的同意无效。</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>images/coaccion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>colocación</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>搭配（词汇学）</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Es más natural decir «tomar una decisión» que «hacer una decisión»; eso es una colocación.</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>说 tomar una decisión 比 hacer una decisión 更自然，这就是搭配。</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>images/colocacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>comparatismo</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>比较研究</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>El comparatismo literario cruza tradiciones.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>文学比较研究跨越不同传统。</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>images/comparatismo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>comunidad discursiva</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>话语共同体</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Cada comunidad discursiva comparte convenciones.</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>每个话语共同体共享惯例。</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>images/comunidad_discursiva_1.jpg</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>concisión</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>简洁</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>La concisión no significa empobrecer el estilo, sino eliminar repeticiones innecesarias.</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>简洁并不意味着风格贫乏，而是去掉不必要的重复。</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>images/concision_1.jpg</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>condensación</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>浓缩；凝练</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>La poesía privilegia la condensación semántica.</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>诗歌讲究语义凝练。</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>images/condensacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>connotación</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>内涵含义；联想义</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>La connotación de «rojo» varía según la cultura y el contexto.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>「rojo」的联想义随文化与语境而变。</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>images/connotacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>construcción social</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>社会建构</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>El género se entiende como construcción social.</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>性别被理解为社会建构。</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>images/construccion_social_1.jpg</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>contingencia</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>偶然性；或然</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>La historia no es pura contingencia.</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>历史并非纯粹偶然。</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>images/contingencia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>corpus</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>语料库</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>El corpus digital permite observar frecuencias reales de uso y colocaciones frecuentes.</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>数字语料库能观察真实使用频率与常见搭配。</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>images/corpus_1.jpg</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>deconstrucción</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>解构</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>La deconstrucción interroga oposiciones binarias.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>解构追问二元对立。</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>images/deconstruccion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>definición operativa</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>操作性定义</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Necesitamos una definición operativa del término.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>我们需要该术语的操作性定义。</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>images/definicion_operativa_1.jpg</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>denotación</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>本义；字面义</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>La denotación de una palabra es su significado literal en el diccionario.</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>词语的本义是词典中的字面意义。</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>images/denotacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>desambiguación</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>消歧</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>La desambiguación depende del contexto.</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>消歧依赖语境。</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>images/desambiguacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>descripción densa</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>深描</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>La antropología usa la descripción densa.</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>人类学使用深描。</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>images/descripcion_densa_1.jpg</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>determinismo</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>决定论</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Critica el determinismo lingüístico extremo.</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>他批判极端语言决定论。</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>images/determinismo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>dialectología</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>方言学</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>La dialectología cartografía variedades regionales.</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>方言学绘制地区变体地图。</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>images/dialectologia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>diglosia</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>双言制</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>En diglosia, una variedad se usa en contextos formales y otra en la vida cotidiana.</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>双言制下，一种变体用于正式场合，另一种用于日常。</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>images/diglosia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>discursivo</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>adj</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>话语的；论述的</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>El análisis discursivo examina poder e ideología en el texto.</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>话语分析考察文本中的权力与意识形态。</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>images/discursivo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disonancia</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>失调；不协调</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Percibimos una disonancia entre decir y hacer.</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>我们感到言行之间的失调。</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>images/disonancia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>empirismo</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>经验主义</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>El empirismo privilegia la observación.</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>经验主义强调观察。</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>images/empirismo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>enfoque cualitativo</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>定性方法</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>El enfoque cualitativo interpreta sentidos.</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>定性方法诠释意义。</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>images/enfoque_cualitativo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>enfoque cuantitativo</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>定量方法</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>El enfoque cuantitativo mide frecuencias.</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>定量方法测量频率。</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>images/enfoque_cuantitativo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>episteme</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>认识型；知识型</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Foucault habla de la episteme de una época.</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>福柯谈论一个时代的认识型。</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>images/episteme_1.jpg</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>epistemología</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>认识论</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>La epistemología pregunta cómo justificamos el conocimiento.</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>认识论追问我们如何为知识辩护。</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>images/epistemologia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>erudición</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>博学；学识</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>El aparato de notas muestra erudición.</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>注释系统显示出博学。</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>images/erudicion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>esquematismo</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>图式化；简略化</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Evita el esquematismo excesivo al resumir.</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>摘要时避免过度图式化。</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>images/esquematismo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>estandarización</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>标准化</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>La estandarización lingüística suele asociarse a la escuela y los medios.</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>语言标准化常与学校及媒体相关。</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>images/estandarizacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>estratificación</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>分层</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>La estratificación social se refleja en el léxico.</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>社会分层反映在词汇上。</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>images/estratificacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>estructuralismo</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>结构主义</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>El estructuralismo analiza relaciones internas.</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>结构主义分析内部关系。</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>images/estructuralismo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>etimología</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>词源</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>La etimología de muchas palabras españolas remonta al latín y, en algunos casos, al árabe.</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>许多西语词的词源可追溯到拉丁语，有些则来自阿拉伯语。</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>images/etimologia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>eufemismo</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>委婉语</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Decir «tercer edad» en lugar de expresiones peyorativas es un eufemismo social común.</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>用「terce edad / 老年」替代贬损说法，是常见的社会委婉语。</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>images/eufemismo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>extrapolación</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>外推</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>La extrapolación de resultados exige cautela.</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>结果外推需谨慎。</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>images/extrapolacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>exégesis</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>经注；详解</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Ofrece una exégesis detallada del pasaje.</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>对段落作了详尽经注式解读。</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>images/exegesis_1.jpg</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>falacia</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>谬误</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Detectar una falacia lógica es clave en el debate académico.</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>识别逻辑谬误是学术辩论的关键。</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>images/falacia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>figuración</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>形象化；修辞形象</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>La figuración poética densifica el sentido.</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>诗歌形象化使意义更密。</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>images/figuracion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>focalización</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>聚焦（叙事）</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>La focalización interna limita lo que sabemos.</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>内聚焦限制我们所知。</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>images/focalizacion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>fonología</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>音系学</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>La fonología estudia el sistema de sonidos de una lengua.</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>音系学研究一种语言的音位系统。</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>images/fonologia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>formalismo</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>形式主义</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>El formalismo atiende la estructura textual.</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>形式主义关注文本结构。</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>images/formalismo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>género discursivo</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>话语体裁</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>El ensayo es un género discursivo académico.</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>论文是一种学术话语体裁。</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>images/genero_discursivo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>hegemonía</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>霸权；主导地位</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Algunos autores hablan de hegemonía cultural cuando ciertos relatos dominan el espacio mediático.</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>某些作者称，当特定叙事主导媒体空间时，便存在文化霸权。</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>images/hegemonia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>hegemonía cultural</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>文化霸权</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Analiza la hegemonía cultural en los medios.</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>他分析媒体中的文化霸权。</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>images/hegemonia_cultural_1.jpg</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>hermenéutica</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>诠释学</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>La hermenéutica literaria interpreta sentidos múltiples del texto.</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>文学诠释学解读文本的多重意义。</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>images/hermeneutica_1.jpg</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>hermetismo</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>晦涩；封闭性</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>El hermetismo del poema exige relectura.</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>诗歌的晦涩要求重读。</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>images/hermetismo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ideología</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>意识形态</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>El ensayo examina cómo la ideología se infiltra en las elecciones léxicas de un texto periodístico.</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>这篇文章检视意识形态如何渗透进新闻文本的用词选择。</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>images/ideologia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>implicatura</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>会话含义（语用学）</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>La implicatura surge cuando el oyente deduce un sentido no dicho a partir del contexto conversacional.</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>当听者根据会话语境推出未明说的含义时，便产生会话含义。</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>images/implicatura_1.jpg</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>interdisciplinario</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>adj</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>跨学科的</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>El enfoque interdisciplinario combina lingüística e historia.</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>跨学科方法结合语言学与历史学。</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>images/interdisciplinario_1.jpg</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>intertextualidad</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>互文性</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>La intertextualidad aparece cuando la novela cita, transforma o dialoga con obras anteriores.</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>当小说引用、改写或与先前作品对话时，便出现互文性。</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>images/intertextualidad_1.jpg</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>lexicografía</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>词典学</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>La lexicografía moderna combina corpus y criterios de uso.</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>现代词典学结合语料与用法标准。</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>images/lexicografia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>matiz</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>细微差别；语感差别</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Hay un matiz importante entre «pedir» y «solicitar»: el segundo suele ser más formal.</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>pedir 与 solicitar 有重要细微差别：后者通常更正式。</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>images/matiz_1.jpg</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>memoria histórica</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>历史记忆</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>El debate sobre la memoria histórica examina cómo una sociedad recuerda conflictos del pasado.</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>关于历史记忆的讨论审视一个社会如何铭记过去的冲突。</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>images/memoria_historica_1.jpg</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>metonimia</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>转喻</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>«La Casa Blanca anunció…» es un caso de metonimia.</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>「白宫宣布…」是转喻的例子。</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>images/metonimia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>paradigma</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>范式</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>El nuevo paradigma educativo pone al estudiante como centro del proceso de aprendizaje.</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>新的教育范式把学生置于学习过程的中心。</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>images/paradigma_1.jpg</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>paradigma teórico</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>理论范式</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>El cambio de paradigma teórico redefine las preguntas de investigación.</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>理论范式转变会重新定义研究问题。</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>images/paradigma_teorico_1.jpg</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>polisemia</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>多义性</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>La polisemia de «banco» incluye el asiento y la institución financiera según el contexto.</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>banco 的多义性包括「长凳」与「银行」，取决于语境。</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>images/polisemia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>pragmatismo</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>实用主义；（亦指）务实态度</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Con pragmatismo, la institución eligió un plan viable en lugar de una reforma ideal pero imposible.</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>出于务实，该机构选择了可行方案，而非理想却不可行的改革。</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>images/pragmatismo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>presuposición</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>预设</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>«Dejó de fumar» contiene la presuposición de que fumaba antes.</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>「他戒烟了」预设他以前抽烟。</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>images/presuposicion_1.jpg</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>préstamo lingüístico</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>借词</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>«Fútbol» es un préstamo lingüístico del inglés que se ha adaptado a la ortografía española.</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>fútbol 是来自英语的借词，并已适应西语拼写。</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>images/prestamo_linguistico_1.jpg</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>redundancia</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>冗余；重复累赘</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Evita la redundancia del tipo «subir hacia arriba»; una sola idea basta si ya está clara.</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>避免「向上爬升」这类冗余；意思已清楚时说一遍即可。</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>images/redundancia_1.jpg</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>semiótica</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>符号学</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>La semiótica analiza signos, símbolos y sistemas de significado.</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>符号学分析符号、象征与意义系统。</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>images/semiotica_1.jpg</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>sesgo</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>偏见；偏差</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Detectar el sesgo en un artículo implica observar qué voces se citan y cuáles se omiten.</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>识别文章中的偏见，要看引用了哪些声音、又忽略了哪些。</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>images/sesgo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>simbolismo</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>象征手法；象征主义</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>El simbolismo del río en la novela sugiere transformación y el paso irreversible del tiempo.</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>小说中河流的象征暗示转变与时间的不可逆流逝。</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>images/simbolismo_1.jpg</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>sociolingüística</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>社会语言学</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>La sociolingüística estudia cómo la clase social, la edad y el género influyen en el habla.</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>社会语言学研究社会阶层、年龄与性别如何影响言语。</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>images/sociolinguistica_1.jpg</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>tabú lingüístico</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>语言禁忌</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>El tabú lingüístico explica por qué ciertas palabras se evitan en contextos formales o familiares.</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>语言禁忌解释了为何某些词在正式或家庭语境中会被回避。</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>images/tabu_linguistico_1.jpg</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>tesis</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>学位论文</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Defendió su tesis doctoral ante un tribunal tras cinco años de investigación de archivo.</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>经过五年档案研究，她在答辩委员会前进行了博士论文答辩。</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>images/tesis_2.jpg</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
           <t>variedad dialectal</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E200" t="inlineStr">
         <is>
           <t>方言变体</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F200" t="inlineStr">
         <is>
           <t>La variedad dialectal del español de México difiere en léxico y entonación del español de España.</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G200" t="inlineStr">
         <is>
           <t>墨西哥西语方言变体在词汇与语调上与西班牙西语有所不同。</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H200" t="inlineStr">
         <is>
           <t>images/variedad_dialectal_1.jpg</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>专八</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ética discursiva</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>话语伦理</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>La ética discursiva exige respeto al otro.</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>话语伦理要求尊重他者。</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>images/etica_discursiva_1.jpg</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
         <is>
           <t>专八</t>
         </is>

--- a/data/content/senses_table_tem8_merged.xlsx
+++ b/data/content/senses_table_tem8_merged.xlsx
@@ -581,7 +581,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ortografía</t>
+          <t>convención</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -601,22 +601,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>拼写</t>
+          <t>协议；约定</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cuidar la ortografía incluye tildes y la diferencia entre b/v o g/j según la regla.</t>
+          <t>Los dos países firmaron una convención para proteger el medio ambiente y los recursos naturales.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>注意拼写包括重音符号，以及按规则区分 b/v、g/j 等。</t>
+          <t>两国签署了一项保护环境和自然资源的协议。</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>images/ortografia_1.jpg</t>
+          <t>images/convencion_1.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -628,7 +628,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>presupuesto</t>
+          <t>escala</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -648,22 +648,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>预算</t>
+          <t>梯子；阶梯</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haz un presupuesto mensual: comida, transporte, material de estudio y un pequeño ahorro.</t>
+          <t>Los pintores usaron una escala para alcanzar la parte alta de la pared del aula.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>做一份月预算：吃饭、交通、学习用品和一点储蓄。</t>
+          <t>油漆工用梯子够到教室墙壁的高处。</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>images/presupuesto_1.jpg</t>
+          <t>images/escala_1.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>traducción</t>
+          <t>estabilidad</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -695,22 +695,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>翻译</t>
+          <t>稳定；稳固；持久性</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>La traducción no es solo cambiar palabras: hay que respetar el sentido y el tono del texto original.</t>
+          <t>La estabilidad económica es fundamental para que los estudiantes puedan terminar sus carreras.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>翻译不只是换词，还要尊重原文的意义与语气。</t>
+          <t>经济稳定对学生完成学业至关重要。</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>images/traduccion_1.jpg</t>
+          <t>images/estabilidad_1.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -722,7 +722,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>acusación</t>
+          <t>evidencia</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -737,39 +737,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>指控；控告</t>
+          <t>明显；证据</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>La acusación carece de pruebas suficientes.</t>
+          <t>No hay evidencia de que el examen fuera demasiado difícil para los estudiantes.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>该指控缺乏足够证据。</t>
+          <t>没有证据表明考试对学生来说太难了。</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>images/acusacion_1.jpg</t>
+          <t>images/evidencia_1.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>afirmación</t>
+          <t>exposición</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,39 +784,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>断言；肯定说法</t>
+          <t>阐述；陈述；展览</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Su afirmación no se sostiene con los datos.</t>
+          <t>La exposición clara de las hipótesis de trabajo es fundamental para lograr una buena nota en la defensa.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>他的断言得不到数据支撑。</t>
+          <t>清晰地阐述工作假说是为了在答辩中取得好成绩的关键基础。</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>images/afirmacion_1.jpg</t>
+          <t>images/exposicion_1.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>alusión</t>
+          <t>interpretación</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -831,39 +831,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>暗指；典故式提及</t>
+          <t>口译；阐释；理解</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El texto hace una alusión a Cervantes.</t>
+          <t>La interpretación de los textos antiguos requiere un profundo conocimiento de la cultura de la época.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>文本暗指塞万提斯。</t>
+          <t>对古籍的阐释需要对那个时代的文化有深刻的了解。</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>images/alusion_1.jpg</t>
+          <t>images/interpretacion_1.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>analogía</t>
+          <t>ortografía</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -878,39 +878,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>类比</t>
+          <t>拼写</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Usa una analogía para explicar el concepto.</t>
+          <t>Cuidar la ortografía incluye tildes y la diferencia entre b/v o g/j según la regla.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>他用类比解释该概念。</t>
+          <t>注意拼写包括重音符号，以及按规则区分 b/v、g/j 等。</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>images/analogia_1.jpg</t>
+          <t>images/ortografia_1.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>anexo</t>
+          <t>presupuesto</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -925,39 +925,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>附录</t>
+          <t>预算</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Los datos completos figuran en el anexo.</t>
+          <t>Haz un presupuesto mensual: comida, transporte, material de estudio y un pequeño ahorro.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>完整数据见附录。</t>
+          <t>做一份月预算：吃饭、交通、学习用品和一点储蓄。</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>images/anexo_1.jpg</t>
+          <t>images/presupuesto_1.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>antonimia</t>
+          <t>traducción</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -972,39 +972,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>反义关系</t>
+          <t>翻译</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alto/bajo es un ejemplo clásico de antonimia gradable.</t>
+          <t>La traducción no es solo cambiar palabras: hay que respetar el sentido y el tono del texto original.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>高/低是典型的可分级反义。</t>
+          <t>翻译不只是换词，还要尊重原文的意义与语气。</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>images/antonimia_1.jpg</t>
+          <t>images/traduccion_1.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>análisis</t>
+          <t>acusación</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1024,34 +1024,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>指控；控告</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El análisis del discurso revela cómo los conectores organizan la argumentación en un editorial.</t>
+          <t>La acusación carece de pruebas suficientes.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>话语分析揭示连接词如何在社论中组织论证结构。</t>
+          <t>该指控缺乏足够证据。</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>images/analisis_1.jpg</t>
+          <t>images/acusacion_1.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>专八|专四</t>
+          <t>专八</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>aproximación</t>
+          <t>afirmación</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1071,22 +1071,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>方法；进路；接近</t>
+          <t>断言；肯定说法</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Proponemos una aproximación interdisciplinaria.</t>
+          <t>Su afirmación no se sostiene con los datos.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>我们提出跨学科进路。</t>
+          <t>他的断言得不到数据支撑。</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>images/aproximacion_1.jpg</t>
+          <t>images/afirmacion_1.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1098,7 +1098,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>argumentación</t>
+          <t>alusión</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1118,22 +1118,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>论证；论述</t>
+          <t>暗指；典故式提及</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>La argumentación del ensayo debe presentar pruebas y contraargumentos.</t>
+          <t>El texto hace una alusión a Cervantes.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>论文的论证应提出证据与反驳。</t>
+          <t>文本暗指塞万提斯。</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>images/argumentacion_1.jpg</t>
+          <t>images/alusion_1.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1145,7 +1145,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>arqueología</t>
+          <t>analogía</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1165,22 +1165,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>考古学</t>
+          <t>类比</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>La arqueología aporta datos materiales sobre el pasado.</t>
+          <t>Usa una analogía para explicar el concepto.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>考古学为过去提供物质证据。</t>
+          <t>他用类比解释该概念。</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>images/arqueologia_1.jpg</t>
+          <t>images/analogia_1.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1192,7 +1192,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>artefacto</t>
+          <t>anexo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1212,22 +1212,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>人工制品；产物</t>
+          <t>附录</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El texto es un artefacto cultural de su época.</t>
+          <t>Los datos completos figuran en el anexo.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>文本是其时代的文化产物。</t>
+          <t>完整数据见附录。</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>images/artefacto_1.jpg</t>
+          <t>images/anexo_1.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1239,7 +1239,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bilingüismo</t>
+          <t>antonimia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1259,22 +1259,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>双语能力；双语现象</t>
+          <t>反义关系</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El bilingüismo no implica dominio perfecto de ambas lenguas en todos los registros.</t>
+          <t>Alto/bajo es un ejemplo clásico de antonimia gradable.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>双语并不意味着两种语言在一切语体上都完美精通。</t>
+          <t>高/低是典型的可分级反义。</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>images/bilinguismo_1.jpg</t>
+          <t>images/antonimia_1.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1286,7 +1286,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>categoría</t>
+          <t>análisis</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1306,34 +1306,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>范畴；类别</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hay que definir cada categoría con precisión.</t>
+          <t>El análisis del discurso revela cómo los conectores organizan la argumentación en un editorial.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>必须精确界定每一范畴。</t>
+          <t>话语分析揭示连接词如何在社论中组织论证结构。</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>images/categoria_1.jpg</t>
+          <t>images/analisis_1.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>causalidad</t>
+          <t>aproximación</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1353,22 +1353,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>因果关系</t>
+          <t>方法；进路；接近</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Correlación no implica necesariamente causalidad.</t>
+          <t>Proponemos una aproximación interdisciplinaria.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>相关并不必然意味着因果。</t>
+          <t>我们提出跨学科进路。</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>images/causalidad_1.jpg</t>
+          <t>images/aproximacion_1.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1380,7 +1380,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cláusula</t>
+          <t>argumentación</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1400,22 +1400,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>从句；条款</t>
+          <t>论证；论述</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Analiza la cláusula subordinada del periodo.</t>
+          <t>La argumentación del ensayo debe presentar pruebas y contraargumentos.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>分析该句中的从属从句。</t>
+          <t>论文的论证应提出证据与反驳。</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>images/clausula_1.jpg</t>
+          <t>images/argumentacion_1.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>codificación</t>
+          <t>arqueología</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1447,22 +1447,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>编码</t>
+          <t>考古学</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>La codificación de los datos sigue un protocolo.</t>
+          <t>La arqueología aporta datos materiales sobre el pasado.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>数据编码遵循协议。</t>
+          <t>考古学为过去提供物质证据。</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>images/codificacion_1.jpg</t>
+          <t>images/arqueologia_1.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1474,7 +1474,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cognición</t>
+          <t>artefacto</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1494,22 +1494,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>认知</t>
+          <t>人工制品；产物</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>La cognición humana procesa el lenguaje en red.</t>
+          <t>El texto es un artefacto cultural de su época.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>人类认知以网络方式处理语言。</t>
+          <t>文本是其时代的文化产物。</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>images/cognicion_1.jpg</t>
+          <t>images/artefacto_1.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>coherencia</t>
+          <t>bilingüismo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>连贯；条理</t>
+          <t>双语能力；双语现象</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La coherencia textual depende de que cada párrafo avance la idea central sin contradicciones.</t>
+          <t>El bilingüismo no implica dominio perfecto de ambas lenguas en todos los registros.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>篇章连贯取决于每一段推进中心思想且不自相矛盾。</t>
+          <t>双语并不意味着两种语言在一切语体上都完美精通。</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>images/coherencia_1.jpg</t>
+          <t>images/bilinguismo_1.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cohesión</t>
+          <t>categoría</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1588,22 +1588,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>衔接（语言学术语）</t>
+          <t>范畴；类别</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Los pronombres y los conectores aportan cohesión al unir oraciones dentro del mismo párrafo.</t>
+          <t>Hay que definir cada categoría con precisión.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>代词与连接词通过把句间关系连起来，带来篇章衔接。</t>
+          <t>必须精确界定每一范畴。</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>images/cohesion_1.jpg</t>
+          <t>images/categoria_1.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1615,7 +1615,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>colonización</t>
+          <t>causalidad</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1635,22 +1635,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>殖民</t>
+          <t>因果关系</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>La colonización dejó huellas lingüísticas profundas.</t>
+          <t>Correlación no implica necesariamente causalidad.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>殖民留下深刻的语言痕迹。</t>
+          <t>相关并不必然意味着因果。</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>images/colonizacion_1.jpg</t>
+          <t>images/causalidad_1.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1662,7 +1662,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>competencia</t>
+          <t>cláusula</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1682,22 +1682,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>能力；（语言）能力</t>
+          <t>从句；条款</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>La competencia comunicativa incluye saber qué decir, cómo decirlo y cuándo callar.</t>
+          <t>Analiza la cláusula subordinada del periodo.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>交际能力包括知道说什么、怎么说，以及何时保持沉默。</t>
+          <t>分析该句中的从属从句。</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>images/competencia_1.jpg</t>
+          <t>images/clausula_1.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1709,12 +1709,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>competencia</t>
+          <t>codificación</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1729,22 +1729,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>竞争；竞赛</t>
+          <t>编码</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>La competencia entre empresas tecnológicas acelera la innovación, pero también genera presión laboral.</t>
+          <t>La codificación de los datos sigue un protocolo.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>科技企业间的竞争加速创新，但也带来职场压力。</t>
+          <t>数据编码遵循协议。</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>images/competencia_2.jpg</t>
+          <t>images/codificacion_1.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>complejidad</t>
+          <t>cognición</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1776,22 +1776,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>复杂性</t>
+          <t>认知</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>La complejidad del fenómeno exige varios enfoques.</t>
+          <t>La cognición humana procesa el lenguaje en red.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>现象的复杂性要求多种方法。</t>
+          <t>人类认知以网络方式处理语言。</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>images/complejidad_1.jpg</t>
+          <t>images/cognicion_1.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>compromiso</t>
+          <t>coherencia</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1823,22 +1823,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>承诺；介入</t>
+          <t>连贯；条理</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El texto muestra un compromiso ético.</t>
+          <t>La coherencia textual depende de que cada párrafo avance la idea central sin contradicciones.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>文本显示出伦理介入。</t>
+          <t>篇章连贯取决于每一段推进中心思想且不自相矛盾。</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>images/compromiso_1.jpg</t>
+          <t>images/coherencia_1.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1850,7 +1850,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>conciliación</t>
+          <t>cohesión</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1870,22 +1870,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>调解；和解</t>
+          <t>衔接（语言学术语）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Buscan la conciliación de intereses opuestos.</t>
+          <t>Los pronombres y los conectores aportan cohesión al unir oraciones dentro del mismo párrafo.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>他们寻求对立利益的和解。</t>
+          <t>代词与连接词通过把句间关系连起来，带来篇章衔接。</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>images/conciliacion_1.jpg</t>
+          <t>images/cohesion_1.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>conclusión</t>
+          <t>colonización</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1917,22 +1917,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>结论</t>
+          <t>殖民</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>En la conclusión no introduzcas datos nuevos; resume y señala límites o futuras líneas de trabajo.</t>
+          <t>La colonización dejó huellas lingüísticas profundas.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>结论部分不要引入新数据；应总结并指出局限或未来研究方向。</t>
+          <t>殖民留下深刻的语言痕迹。</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>images/conclusion_1.jpg</t>
+          <t>images/colonizacion_1.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1944,7 +1944,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>configuración</t>
+          <t>competencia</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1964,22 +1964,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>构型；配置</t>
+          <t>能力；（语言）能力</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Analizamos la configuración del relato.</t>
+          <t>La competencia comunicativa incluye saber qué decir, cómo decirlo y cuándo callar.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>我们分析叙事构型。</t>
+          <t>交际能力包括知道说什么、怎么说，以及何时保持沉默。</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>images/configuracion_1.jpg</t>
+          <t>images/competencia_1.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1991,12 +1991,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>competencia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2011,22 +2011,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>共识</t>
+          <t>竞争；竞赛</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>No hay consenso sobre la definición.</t>
+          <t>La competencia entre empresas tecnológicas acelera la innovación, pero también genera presión laboral.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>关于定义尚无共识。</t>
+          <t>科技企业间的竞争加速创新，但也带来职场压力。</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>images/consenso_1.jpg</t>
+          <t>images/competencia_2.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2038,7 +2038,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>consistencia</t>
+          <t>complejidad</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2058,22 +2058,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>一致性；连贯严谨</t>
+          <t>复杂性</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>La consistencia argumentativa es esencial.</t>
+          <t>La complejidad del fenómeno exige varios enfoques.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>论证一致性至关重要。</t>
+          <t>现象的复杂性要求多种方法。</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>images/consistencia_1.jpg</t>
+          <t>images/complejidad_1.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2085,7 +2085,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>contaminación</t>
+          <t>compromiso</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2105,22 +2105,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>污染；（也指）干扰</t>
+          <t>承诺；介入</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hay contaminación entre variedades en contacto.</t>
+          <t>El texto muestra un compromiso ético.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>接触中的变体之间存在干扰。</t>
+          <t>文本显示出伦理介入。</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>images/contaminacion_1.jpg</t>
+          <t>images/compromiso_1.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>contextualizar</t>
+          <t>conciliación</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>v</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2152,22 +2152,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>置于语境；语境化</t>
+          <t>调解；和解</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hay que contextualizar la cita antes de analizarla.</t>
+          <t>Buscan la conciliación de intereses opuestos.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>分析引文前须先置于语境。</t>
+          <t>他们寻求对立利益的和解。</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>images/contextualizar_1.jpg</t>
+          <t>images/conciliacion_1.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2179,7 +2179,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>contradicción</t>
+          <t>conclusión</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2199,22 +2199,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>矛盾</t>
+          <t>结论</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>El texto cae en contradicción entre el primer y el último párrafo.</t>
+          <t>En la conclusión no introduzcas datos nuevos; resume y señala límites o futuras líneas de trabajo.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>文本在首段与末段之间自相矛盾。</t>
+          <t>结论部分不要引入新数据；应总结并指出局限或未来研究方向。</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>images/contradiccion_1.jpg</t>
+          <t>images/conclusion_1.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2226,7 +2226,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>contraposición</t>
+          <t>configuración</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2246,22 +2246,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>对照；对立设置</t>
+          <t>构型；配置</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>La contraposición de personajes estructura la novela.</t>
+          <t>Analizamos la configuración del relato.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>人物对照构成小说结构。</t>
+          <t>我们分析叙事构型。</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>images/contraposicion_1.jpg</t>
+          <t>images/configuracion_1.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2273,7 +2273,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>convención</t>
+          <t>consenso</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2293,22 +2293,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>惯例；公约</t>
+          <t>共识</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rompe la convención narrativa del final cerrado.</t>
+          <t>No hay consenso sobre la definición.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>它打破封闭结局的叙事惯例。</t>
+          <t>关于定义尚无共识。</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>images/convencion_1.jpg</t>
+          <t>images/consenso_1.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2320,7 +2320,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>correlación</t>
+          <t>consistencia</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2340,22 +2340,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>相关；相关性</t>
+          <t>一致性；连贯严谨</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hay correlación entre horas de estudio y rendimiento.</t>
+          <t>La consistencia argumentativa es esencial.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>学习时长与成绩之间存在相关。</t>
+          <t>论证一致性至关重要。</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>images/correlacion_1.jpg</t>
+          <t>images/consistencia_1.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>corroborar</t>
+          <t>contaminación</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>v</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2387,22 +2387,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>证实；确证</t>
+          <t>污染；（也指）干扰</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Los datos corroboran la hipótesis.</t>
+          <t>Hay contaminación entre variedades en contacto.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>数据证实了该假设。</t>
+          <t>接触中的变体之间存在干扰。</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>images/corroborar_1.jpg</t>
+          <t>images/contaminacion_1.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2414,7 +2414,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>credibilidad</t>
+          <t>contextualizar</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>v</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2434,22 +2434,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>可信度</t>
+          <t>置于语境；语境化</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>La fuente pierde credibilidad sin referencias.</t>
+          <t>Hay que contextualizar la cita antes de analizarla.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>缺少出处会降低来源可信度。</t>
+          <t>分析引文前须先置于语境。</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>images/credibilidad_1.jpg</t>
+          <t>images/contextualizar_1.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>criterio</t>
+          <t>contradicción</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>标准；准则</t>
+          <t>矛盾</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hay que definir criterios claros de evaluación.</t>
+          <t>El texto cae en contradicción entre el primer y el último párrafo.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>必须明确评价标准。</t>
+          <t>文本在首段与末段之间自相矛盾。</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>images/criterio_1.jpg</t>
+          <t>images/contradiccion_1.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>专八|专四</t>
+          <t>专八</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>crítica</t>
+          <t>contraposición</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2528,22 +2528,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>评论；批评</t>
+          <t>对照；对立设置</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>La crítica literaria no solo juzga si un libro «gusta», sino cómo construye sentido y estilo.</t>
+          <t>La contraposición de personajes estructura la novela.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>文学批评不只判断书是否「好看」，还分析它如何构建意义与风格。</t>
+          <t>人物对照构成小说结构。</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>images/critica_1.jpg</t>
+          <t>images/contraposicion_1.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2555,7 +2555,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cuestionario</t>
+          <t>correlación</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2575,22 +2575,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>问卷</t>
+          <t>相关；相关性</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>El cuestionario mide actitudes lingüísticas.</t>
+          <t>Hay correlación entre horas de estudio y rendimiento.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>问卷测量语言态度。</t>
+          <t>学习时长与成绩之间存在相关。</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>images/cuestionario_1.jpg</t>
+          <t>images/correlacion_1.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>deducción</t>
+          <t>corroborar</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>v</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2622,34 +2622,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>演绎</t>
+          <t>证实；确证</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>La deducción parte de premisas generales.</t>
+          <t>Los datos corroboran la hipótesis.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>演绎从一般前提出发。</t>
+          <t>数据证实了该假设。</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>images/deduccion_1.jpg</t>
+          <t>images/corroborar_1.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>专八|专四</t>
+          <t>专八</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>delimitación</t>
+          <t>credibilidad</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2669,22 +2669,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>界定；划界</t>
+          <t>可信度</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>La delimitación del objeto de estudio es clave.</t>
+          <t>La fuente pierde credibilidad sin referencias.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>研究对象的界定很关键。</t>
+          <t>缺少出处会降低来源可信度。</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>images/delimitacion_1.jpg</t>
+          <t>images/credibilidad_1.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2696,7 +2696,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>demografía</t>
+          <t>criterio</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2716,34 +2716,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>人口学；人口结构</t>
+          <t>标准；准则；判断依据</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>La demografía explica cambios en el uso lingüístico.</t>
+          <t>El profesor utiliza varios criterios para evaluar la calidad de nuestros trabajos escritos.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>人口结构解释语言使用变化。</t>
+          <t>老师使用多种标准来评估我们书面作业的质量。</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>images/demografia_1.jpg</t>
+          <t>images/criterio_1.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>crítica</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2763,22 +2763,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>迁移；转移</t>
+          <t>评论；批评</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>El desplazamiento semántico altera el significado.</t>
+          <t>La crítica literaria no solo juzga si un libro «gusta», sino cómo construye sentido y estilo.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>语义转移改变意义。</t>
+          <t>文学批评不只判断书是否「好看」，还分析它如何构建意义与风格。</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>images/desplazamiento_1.jpg</t>
+          <t>images/critica_1.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2790,7 +2790,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dialecto</t>
+          <t>cuestionario</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2810,22 +2810,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>方言</t>
+          <t>问卷</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>El andaluz es un dialecto del español peninsular.</t>
+          <t>El cuestionario mide actitudes lingüísticas.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>安达卢西亚语是半岛西班牙语的一种方言。</t>
+          <t>问卷测量语言态度。</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>images/dialecto_1.jpg</t>
+          <t>images/cuestionario_1.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2837,7 +2837,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>dicotomía</t>
+          <t>deducción</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2857,34 +2857,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>二分法</t>
+          <t>推断；推论；演绎</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Evita una dicotomía demasiado rígida.</t>
+          <t>Tu deducción lógica sobre el final de la novela española sorprendió gratamente a toda la clase.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>避免过于僵硬的二分。</t>
+          <t>你对这部西班牙小说结局的逻辑推断让全班同学感到惊喜和钦佩。</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>images/dicotomia_1.jpg</t>
+          <t>images/deduccion_1.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>diferenciación</t>
+          <t>delimitación</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2904,22 +2904,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>分化；区分</t>
+          <t>界定；划界</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hay diferenciación estilística entre géneros.</t>
+          <t>La delimitación del objeto de estudio es clave.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>体裁之间存在风格分化。</t>
+          <t>研究对象的界定很关键。</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>images/diferenciacion_1.jpg</t>
+          <t>images/delimitacion_1.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2931,7 +2931,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>discurso</t>
+          <t>demografía</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>话语；演说</t>
+          <t>人口学；人口结构</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>El discurso político usa metáforas y repeticiones para persuadir a una audiencia diversa.</t>
+          <t>La demografía explica cambios en el uso lingüístico.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>政治演说运用隐喻与重复，以说服多元听众。</t>
+          <t>人口结构解释语言使用变化。</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>images/discurso_1.jpg</t>
+          <t>images/demografia_1.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>distribución</t>
+          <t>desplazamiento</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2998,22 +2998,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>分布</t>
+          <t>迁移；转移</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Estudiamos la distribución geográfica del rasgo.</t>
+          <t>El desplazamiento semántico altera el significado.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>我们研究该特征的地理分布。</t>
+          <t>语义转移改变意义。</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>images/distribucion_1.jpg</t>
+          <t>images/desplazamiento_1.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3025,7 +3025,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>divergencia</t>
+          <t>dialecto</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3045,22 +3045,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>分歧；分化</t>
+          <t>方言</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>La divergencia dialectal aumenta con la distancia.</t>
+          <t>El andaluz es un dialecto del español peninsular.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>方言分歧随距离增大。</t>
+          <t>安达卢西亚语是半岛西班牙语的一种方言。</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>images/divergencia_1.jpg</t>
+          <t>images/dialecto_1.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3072,7 +3072,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>diversidad</t>
+          <t>dicotomía</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3092,22 +3092,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>多样性</t>
+          <t>二分法</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>La diversidad lingüística del mundo hispánico es un patrimonio que conviene preservar y estudiar.</t>
+          <t>Evita una dicotomía demasiado rígida.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>西语世界的语言多样性是值得保护与研究的遗产。</t>
+          <t>避免过于僵硬的二分。</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>images/diversidad_1.jpg</t>
+          <t>images/dicotomia_1.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>documentación</t>
+          <t>diferenciación</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3139,22 +3139,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>文献；文档工作</t>
+          <t>分化；区分</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>La documentación de lenguas en peligro es urgente.</t>
+          <t>Hay diferenciación estilística entre géneros.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>濒危语言文献工作紧迫。</t>
+          <t>体裁之间存在风格分化。</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>images/documentacion_1.jpg</t>
+          <t>images/diferenciacion_1.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3166,7 +3166,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>elaboración</t>
+          <t>discurso</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>加工；阐述</t>
+          <t>话语；演说</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>La elaboración del argumento requiere ejemplos.</t>
+          <t>El discurso político usa metáforas y repeticiones para persuadir a una audiencia diversa.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>论证的阐述需要例子。</t>
+          <t>政治演说运用隐喻与重复，以说服多元听众。</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>images/elaboracion_1.jpg</t>
+          <t>images/discurso_1.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3213,7 +3213,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>elipsis</t>
+          <t>distribución</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3233,22 +3233,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>省略</t>
+          <t>分布</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>La elipsis evita repeticiones innecesarias.</t>
+          <t>Estudiamos la distribución geográfica del rasgo.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>省略避免不必要的重复。</t>
+          <t>我们研究该特征的地理分布。</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>images/elipsis_1.jpg</t>
+          <t>images/distribucion_1.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3260,7 +3260,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>empatía</t>
+          <t>divergencia</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3280,22 +3280,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>共情</t>
+          <t>分歧；分化</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>La empatía del narrador acerca al lector.</t>
+          <t>La divergencia dialectal aumenta con la distancia.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>叙述者的共情拉近读者。</t>
+          <t>方言分歧随距离增大。</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>images/empatia_1.jpg</t>
+          <t>images/divergencia_1.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3307,7 +3307,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>encuesta</t>
+          <t>diversidad</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3327,22 +3327,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>调查</t>
+          <t>多样性</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>La encuesta recoge datos de percepción.</t>
+          <t>La diversidad lingüística del mundo hispánico es un patrimonio que conviene preservar y estudiar.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>调查收集感知数据。</t>
+          <t>西语世界的语言多样性是值得保护与研究的遗产。</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>images/encuesta_1.jpg</t>
+          <t>images/diversidad_1.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3354,7 +3354,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>enfoque</t>
+          <t>documentación</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3374,22 +3374,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>切入角度；方法焦点</t>
+          <t>文献；文档工作</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>El enfoque comunicativo prioriza el uso real de la lengua frente a la memorización de reglas.</t>
+          <t>La documentación de lenguas en peligro es urgente.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>交际法优先真实使用语言，而非死记规则。</t>
+          <t>濒危语言文献工作紧迫。</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>images/enfoque_1.jpg</t>
+          <t>images/documentacion_1.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3401,7 +3401,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>entorno</t>
+          <t>elaboración</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3421,22 +3421,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>环境；语境环境</t>
+          <t>加工；阐述</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>El entorno sociolingüístico condiciona el habla.</t>
+          <t>La elaboración del argumento requiere ejemplos.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>社会语言环境制约说话方式。</t>
+          <t>论证的阐述需要例子。</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>images/entorno_1.jpg</t>
+          <t>images/elaboracion_1.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3448,7 +3448,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>enumeración</t>
+          <t>elipsis</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3468,22 +3468,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>列举</t>
+          <t>省略</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>La enumeración refuerza la idea principal.</t>
+          <t>La elipsis evita repeticiones innecesarias.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>列举强化中心思想。</t>
+          <t>省略避免不必要的重复。</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>images/enumeracion_1.jpg</t>
+          <t>images/elipsis_1.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3495,7 +3495,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>enunciado</t>
+          <t>empatía</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3515,22 +3515,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>表述；话语单位</t>
+          <t>共情</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cada enunciado realiza un acto de habla en contexto.</t>
+          <t>La empatía del narrador acerca al lector.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>每个表述在语境中完成一个言语行为。</t>
+          <t>叙述者的共情拉近读者。</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>images/enunciado_1.jpg</t>
+          <t>images/empatia_1.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>equivalencia</t>
+          <t>encuesta</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3562,22 +3562,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>对等</t>
+          <t>调查</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Busca equivalencia funcional en la traducción.</t>
+          <t>La encuesta recoge datos de percepción.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>翻译中寻求功能对等。</t>
+          <t>调查收集感知数据。</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>images/equivalencia_1.jpg</t>
+          <t>images/encuesta_1.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3589,7 +3589,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>escala</t>
+          <t>enfoque</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3609,22 +3609,22 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>量表；尺度</t>
+          <t>切入角度；方法焦点</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Usamos una escala Likert de cinco puntos.</t>
+          <t>El enfoque comunicativo prioriza el uso real de la lengua frente a la memorización de reglas.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>我们使用五点李克特量表。</t>
+          <t>交际法优先真实使用语言，而非死记规则。</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>images/escala_1.jpg</t>
+          <t>images/enfoque_1.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3636,7 +3636,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>estabilidad</t>
+          <t>entorno</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3656,22 +3656,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>稳定性</t>
+          <t>环境；语境环境</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>La norma busca estabilidad ortográfica.</t>
+          <t>El entorno sociolingüístico condiciona el habla.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>规范追求拼写稳定。</t>
+          <t>社会语言环境制约说话方式。</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>images/estabilidad_1.jpg</t>
+          <t>images/entorno_1.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3683,7 +3683,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>estigma</t>
+          <t>enumeración</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3703,22 +3703,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>污名</t>
+          <t>列举</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>El estigma lingüístico afecta a hablantes.</t>
+          <t>La enumeración refuerza la idea principal.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>语言污名影响使用者。</t>
+          <t>列举强化中心思想。</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>images/estigma_1.jpg</t>
+          <t>images/enumeracion_1.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3730,7 +3730,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>estilo</t>
+          <t>enunciado</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3750,22 +3750,22 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>风格；文风</t>
+          <t>表述；话语单位</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>El estilo del autor se reconoce por frases largas, adjetivos precisos y un humor contenido.</t>
+          <t>Cada enunciado realiza un acto de habla en contexto.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>作者的文风以长句、精确形容词与克制的幽默为特征。</t>
+          <t>每个表述在语境中完成一个言语行为。</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>images/estilo_1.jpg</t>
+          <t>images/enunciado_1.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3777,7 +3777,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>etnografía</t>
+          <t>equivalencia</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3797,22 +3797,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>民族志</t>
+          <t>对等</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>La etnografía observa prácticas situadas.</t>
+          <t>Busca equivalencia funcional en la traducción.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>民族志观察情境中的实践。</t>
+          <t>翻译中寻求功能对等。</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>images/etnografia_1.jpg</t>
+          <t>images/equivalencia_1.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3824,7 +3824,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>evaluación</t>
+          <t>estigma</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3844,34 +3844,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>评价；评估</t>
+          <t>污名</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>La evaluación formativa guía el aprendizaje.</t>
+          <t>El estigma lingüístico afecta a hablantes.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>形成性评价引导学习。</t>
+          <t>语言污名影响使用者。</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>images/evaluacion_1.jpg</t>
+          <t>images/estigma_1.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>专八|专四</t>
+          <t>专八</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>evidencia</t>
+          <t>estilo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3891,22 +3891,22 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>证据</t>
+          <t>风格；文风</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>La evidencia empírica respalda la hipótesis principal.</t>
+          <t>El estilo del autor se reconoce por frases largas, adjetivos precisos y un humor contenido.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>经验证据支持主要假设。</t>
+          <t>作者的文风以长句、精确形容词与克制的幽默为特征。</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>images/evidencia_1.jpg</t>
+          <t>images/estilo_1.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3918,7 +3918,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>expectativa</t>
+          <t>etnografía</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3938,22 +3938,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>期待</t>
+          <t>民族志</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rompe la expectativa del lector.</t>
+          <t>La etnografía observa prácticas situadas.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>它打破了读者的期待。</t>
+          <t>民族志观察情境中的实践。</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>images/expectativa_1.jpg</t>
+          <t>images/etnografia_1.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3965,7 +3965,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>explicación</t>
+          <t>evaluación</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3985,34 +3985,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>解释</t>
+          <t>评估；考试；评价</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>La explicación aclara el procedimiento.</t>
+          <t>La evaluación final del curso de español se basa tanto en la participación diaria como en el examen escrito.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>解释澄清了步骤。</t>
+          <t>西语课程的期末评估既基于日常参与度，也基于笔试成绩。</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>images/explicacion_1.jpg</t>
+          <t>images/evaluacion_1.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>exposición</t>
+          <t>expectativa</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4032,34 +4032,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>说明文；陈述</t>
+          <t>期待</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>La exposición presenta hechos con claridad.</t>
+          <t>Rompe la expectativa del lector.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>说明文清晰陈述事实。</t>
+          <t>它打破了读者的期待。</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>images/exposicion_1.jpg</t>
+          <t>images/expectativa_1.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>专八|专四</t>
+          <t>专八</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>fiabilidad</t>
+          <t>explicación</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4079,22 +4079,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>信度</t>
+          <t>解释</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Comprobamos la fiabilidad del instrumento.</t>
+          <t>La explicación aclara el procedimiento.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>我们检验工具信度。</t>
+          <t>解释澄清了步骤。</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>images/fiabilidad_1.jpg</t>
+          <t>images/explicacion_1.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4106,7 +4106,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>fonética</t>
+          <t>fiabilidad</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>语音学</t>
+          <t>信度</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>La fonética describe cómo se producen los sonidos.</t>
+          <t>Comprobamos la fiabilidad del instrumento.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>语音学描述语音如何发出。</t>
+          <t>我们检验工具信度。</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>images/fonetica_1.jpg</t>
+          <t>images/fiabilidad_1.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>fragmentación</t>
+          <t>fonética</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4173,22 +4173,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>碎片化</t>
+          <t>语音学</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>La fragmentación narrativa refleja crisis.</t>
+          <t>La fonética describe cómo se producen los sonidos.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>叙事碎片化反映危机。</t>
+          <t>语音学描述语音如何发出。</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>images/fragmentacion_1.jpg</t>
+          <t>images/fonetica_1.jpg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4200,7 +4200,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>fuente</t>
+          <t>fragmentación</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4220,22 +4220,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>来源；（也指）泉水</t>
+          <t>碎片化</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cita siempre la fuente primaria cuando uses datos estadísticos en tu trabajo de investigación.</t>
+          <t>La fragmentación narrativa refleja crisis.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>在研究作业中使用统计数据时，务必引用原始来源。</t>
+          <t>叙事碎片化反映危机。</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>images/fuente_1.jpg</t>
+          <t>images/fragmentacion_1.jpg</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4267,22 +4267,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>泉水；喷泉</t>
+          <t>来源；（也指）泉水</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nos sentamos junto a la fuente de la plaza mientras repasábamos las preguntas del examen oral.</t>
+          <t>Cita siempre la fuente primaria cuando uses datos estadísticos en tu trabajo de investigación.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>我们坐在广场喷泉旁复习口语考试的问题。</t>
+          <t>在研究作业中使用统计数据时，务必引用原始来源。</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>images/fuente_2.jpg</t>
+          <t>images/fuente_1.jpg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4294,12 +4294,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>generalización</t>
+          <t>fuente</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4314,22 +4314,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>概括</t>
+          <t>泉水；喷泉</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Evita generalizaciones apresuradas.</t>
+          <t>Nos sentamos junto a la fuente de la plaza mientras repasábamos las preguntas del examen oral.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>避免仓促概括。</t>
+          <t>我们坐在广场喷泉旁复习口语考试的问题。</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>images/generalizacion_1.jpg</t>
+          <t>images/fuente_2.jpg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4341,7 +4341,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>globalización</t>
+          <t>generalización</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4361,22 +4361,22 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>全球化</t>
+          <t>概括</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>La globalización facilita el intercambio cultural, aunque también plantea retos a las identidades locales.</t>
+          <t>Evita generalizaciones apresuradas.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>全球化促进文化交流，同时也给地方认同带来挑战。</t>
+          <t>避免仓促概括。</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>images/globalizacion_1.jpg</t>
+          <t>images/generalizacion_1.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4388,7 +4388,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>glosario</t>
+          <t>globalización</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4408,22 +4408,22 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>术语表</t>
+          <t>全球化</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>El glosario define los términos técnicos del capítulo.</t>
+          <t>La globalización facilita el intercambio cultural, aunque también plantea retos a las identidades locales.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>术语表界定本章技术用语。</t>
+          <t>全球化促进文化交流，同时也给地方认同带来挑战。</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>images/glosario_1.jpg</t>
+          <t>images/globalizacion_1.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4435,7 +4435,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>hipotético</t>
+          <t>glosario</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>adj</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4455,22 +4455,22 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>假设的；假想的</t>
+          <t>术语表</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Partimos de un escenario hipotético para el debate.</t>
+          <t>El glosario define los términos técnicos del capítulo.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>我们从假想情景展开辩论。</t>
+          <t>术语表界定本章技术用语。</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>images/hipotetico_1.jpg</t>
+          <t>images/glosario_1.jpg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4482,7 +4482,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>hipótesis</t>
+          <t>hipotético</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>adj</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4502,22 +4502,22 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>假设；假说</t>
+          <t>假设的；假想的</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>La hipótesis del estudio sostiene que el contacto frecuente con hablantes nativos acelera la fluidez.</t>
+          <t>Partimos de un escenario hipotético para el debate.</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>该研究假设：与母语者频繁接触会加快流利度提升。</t>
+          <t>我们从假想情景展开辩论。</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>images/hipotesis_1.jpg</t>
+          <t>images/hipotetico_1.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4529,7 +4529,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>homónimo</t>
+          <t>hipótesis</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4549,22 +4549,22 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>同音/同形异义词</t>
+          <t>假设；假说</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>«Banco» (asiento) y «banco» (entidad financiera) son homónimos: misma forma, sentidos distintos.</t>
+          <t>La hipótesis del estudio sostiene que el contacto frecuente con hablantes nativos acelera la fluidez.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>banco（长凳）与 banco（金融机构）是同形异义词：形式相同、意义不同。</t>
+          <t>该研究假设：与母语者频繁接触会加快流利度提升。</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>images/homonimo_1.jpg</t>
+          <t>images/hipotesis_1.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4576,7 +4576,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>identidad</t>
+          <t>homónimo</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4596,22 +4596,22 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>身份；认同</t>
+          <t>同音/同形异义词</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>La identidad cultural se construye con la lengua, la memoria familiar y las prácticas cotidianas.</t>
+          <t>«Banco» (asiento) y «banco» (entidad financiera) son homónimos: misma forma, sentidos distintos.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>文化认同由语言、家庭记忆与日常实践共同建构。</t>
+          <t>banco（长凳）与 banco（金融机构）是同形异义词：形式相同、意义不同。</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>images/identidad_1.jpg</t>
+          <t>images/homonimo_1.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4623,7 +4623,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>inferencia</t>
+          <t>identidad</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4643,22 +4643,22 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>推断；推理</t>
+          <t>身份；认同</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Aunque el texto no lo diga explícitamente, por inferencia entendemos que el personaje está en crisis.</t>
+          <t>La identidad cultural se construye con la lengua, la memoria familiar y las prácticas cotidianas.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>虽然文本未明说，通过推断我们明白人物正陷入危机。</t>
+          <t>文化认同由语言、家庭记忆与日常实践共同建构。</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>images/inferencia_1.jpg</t>
+          <t>images/identidad_1.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4670,7 +4670,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>innovación</t>
+          <t>inferencia</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4690,22 +4690,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>创新</t>
+          <t>推断；推理</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>La innovación educativa no es solo usar apps, sino rediseñar actividades para un aprendizaje activo.</t>
+          <t>Aunque el texto no lo diga explícitamente, por inferencia entendemos que el personaje está en crisis.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>教育创新不只是用 App，而是重新设计活动以促进主动学习。</t>
+          <t>虽然文本未明说，通过推断我们明白人物正陷入危机。</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>images/innovacion_1.jpg</t>
+          <t>images/inferencia_1.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4717,7 +4717,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>interpretación</t>
+          <t>innovación</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4737,27 +4737,27 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>口译；解读</t>
+          <t>创新</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Su interpretación del poema destaca el tono irónico.</t>
+          <t>La innovación educativa no es solo usar apps, sino rediseñar actividades para un aprendizaje activo.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>他对这首诗的解读突出了反讽语气。</t>
+          <t>教育创新不只是用 App，而是重新设计活动以促进主动学习。</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>images/interpretacion_1.jpg</t>
+          <t>images/innovacion_1.jpg</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>专八|专四</t>
+          <t>专八</t>
         </is>
       </c>
     </row>
@@ -5865,17 +5865,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>综合；综述</t>
+          <t>综合；总结；概要</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>La síntesis reúne las ideas principales sin detalles superfluos.</t>
+          <t>Hacer una síntesis de la lectura es una excelente estrategia para repasar la materia del examen.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>综述汇总主要观点，不含多余细节。</t>
+          <t>对阅读内容做一份概要总结是复习考试科目的绝佳策略。</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">

--- a/data/content/senses_table_tem8_merged.xlsx
+++ b/data/content/senses_table_tem8_merged.xlsx
@@ -5274,7 +5274,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>专八</t>
+          <t>专八|专四</t>
         </is>
       </c>
     </row>
